--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484274_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484274_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8337</v>
+        <v>10.6358</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3647</v>
+        <v>6.3847</v>
       </c>
       <c r="F2" t="n">
-        <v>4.469</v>
+        <v>4.2511</v>
       </c>
       <c r="G2" t="n">
         <v>1.4893</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9387</v>
+        <v>0.7408</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2254</v>
+        <v>-0.2055</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1641</v>
+        <v>0.9462</v>
       </c>
       <c r="V2" t="n">
         <v>6.6476</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.471</v>
+        <v>0.8003</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.9204</v>
+        <v>-2.069</v>
       </c>
       <c r="F3" t="n">
-        <v>5.3914</v>
+        <v>2.8694</v>
       </c>
       <c r="G3" t="n">
-        <v>-5.9549</v>
+        <v>-0.6283</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.4332</v>
+        <v>-0.2637</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.5217</v>
+        <v>-0.3646</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.3063</v>
+        <v>-0.4686</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.9763</v>
+        <v>0.165</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.33</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6485</v>
+        <v>-0.1597</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4569</v>
+        <v>-0.4287</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8083</v>
+        <v>0.269</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1255</v>
+        <v>2.7348</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4063</v>
+        <v>-0.1341</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8202</v>
+        <v>-0.4284</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5861</v>
+        <v>0.2943</v>
       </c>
       <c r="V3" t="n">
-        <v>4.0428</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.3283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7491</v>
+        <v>0.3985</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6845</v>
+        <v>-0.12</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4336</v>
+        <v>0.5185</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6283</v>
+        <v>0.166</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2637</v>
+        <v>0.0312</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3646</v>
+        <v>0.1348</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4686</v>
+        <v>0.0409</v>
       </c>
       <c r="K4" t="n">
-        <v>0.165</v>
+        <v>0.0409</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1597</v>
+        <v>0.1251</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4287</v>
+        <v>-0.0097</v>
       </c>
       <c r="O4" t="n">
-        <v>0.269</v>
+        <v>0.1348</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7348</v>
+        <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1853</v>
+        <v>0.0371</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0438</v>
+        <v>-0.1609</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1415</v>
+        <v>0.1981</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0329</v>
+        <v>-0.3156</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3222</v>
+        <v>-5.0533</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3551</v>
+        <v>4.7377</v>
       </c>
       <c r="G5" t="n">
-        <v>0.166</v>
+        <v>-5.9549</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0312</v>
+        <v>-3.4332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1348</v>
+        <v>-2.5217</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0409</v>
+        <v>-5.3063</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0409</v>
+        <v>-1.9763</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-3.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1251</v>
+        <v>-0.6485</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0097</v>
+        <v>-1.4569</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1348</v>
+        <v>0.8083</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1953</v>
+        <v>3.1255</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3285</v>
+        <v>0.6197</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3631</v>
+        <v>-0.3127</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0346</v>
+        <v>0.9325</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.0428</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.381</v>
+        <v>-0.5929</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2715</v>
+        <v>-1.211</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8905</v>
+        <v>0.6181</v>
       </c>
       <c r="G6" t="n">
         <v>0.4724</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6657</v>
+        <v>0.4539</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1127</v>
+        <v>-0.0522</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7784</v>
+        <v>0.5061</v>
       </c>
       <c r="V6" t="n">
         <v>-2.1052</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4576</v>
+        <v>-1.2415</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.117</v>
+        <v>-0.9553</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3406</v>
+        <v>-0.2861</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1775</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6708</v>
+        <v>-0.4547</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4237</v>
+        <v>-0.262</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2471</v>
+        <v>-0.1926</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8481</v>
+        <v>-1.7059</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2698</v>
+        <v>-2.2093</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4217</v>
+        <v>0.5034</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2836</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3692</v>
+        <v>-0.227</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4237</v>
+        <v>-0.3631</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0545</v>
+        <v>0.1362</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7778</v>
+        <v>-1.7679</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2304</v>
+        <v>-1.1388</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5475</v>
+        <v>-0.6292</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9944</v>
@@ -1156,13 +1156,13 @@
         <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9239000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0894</v>
+        <v>0.0022</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1655</v>
+        <v>0.0838</v>
       </c>
       <c r="V9" t="n">
         <v>0.5545</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0736</v>
+        <v>-2.1604</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5613</v>
+        <v>-1.2439</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5122</v>
+        <v>-0.9164</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5428</v>
+        <v>-1.1846</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7179</v>
+        <v>-0.726</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1751</v>
+        <v>-0.4585</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.4908</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9594</v>
+        <v>0.1023</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6239</v>
+        <v>-0.6937</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7585</v>
+        <v>-0.8283</v>
       </c>
       <c r="O10" t="n">
         <v>0.1346</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2273</v>
+        <v>0.6335</v>
       </c>
       <c r="T10" t="n">
-        <v>0.311</v>
+        <v>0.2236</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0837</v>
+        <v>0.4099</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0982</v>
+        <v>-2.4731</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0728</v>
+        <v>-3.918</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0254</v>
+        <v>1.4449</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1846</v>
+        <v>-1.9175</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.726</v>
+        <v>-1.6204</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4585</v>
+        <v>-0.2971</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4908</v>
+        <v>-0.5946</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1023</v>
+        <v>0.1061</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.7007</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6937</v>
+        <v>-1.3228</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8283</v>
+        <v>-1.7265</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1346</v>
+        <v>0.4037</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>3.3208</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3043</v>
+        <v>-0.4189</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6052</v>
+        <v>-0.4751</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3009</v>
+        <v>0.0562</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3725</v>
+        <v>-3.2892</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4634</v>
+        <v>-2.8042</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0908</v>
+        <v>-0.485</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9175</v>
+        <v>-1.5428</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6204</v>
+        <v>-1.7179</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2971</v>
+        <v>0.1751</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5946</v>
+        <v>-0.9189000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1061</v>
+        <v>-0.9594</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7007</v>
+        <v>0.0405</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3228</v>
+        <v>-0.6239</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7265</v>
+        <v>-0.7585</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4037</v>
+        <v>0.1346</v>
       </c>
       <c r="P12" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.1953</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-3.1255</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.3208</v>
-      </c>
       <c r="S12" t="n">
-        <v>-1.3184</v>
+        <v>0.0117</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0205</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2978</v>
+        <v>-0.0565</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.922099999999999</v>
+        <v>-1.7119</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.5486</v>
+        <v>-14.3381</v>
       </c>
       <c r="F13" t="n">
         <v>12.6264</v>
@@ -1441,7 +1441,7 @@
         <v>-6.743</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.891999999999999</v>
+        <v>-8.892000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>1.2173</v>
@@ -1453,7 +1453,7 @@
         <v>-5.6636</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.030099999999999</v>
+        <v>-9.030100000000001</v>
       </c>
       <c r="O13" t="n">
         <v>3.3664</v>
@@ -1468,13 +1468,13 @@
         <v>17.5807</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1375999999999999</v>
+        <v>1.348</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1763</v>
+        <v>-1.966</v>
       </c>
       <c r="U13" t="n">
-        <v>3.314</v>
+        <v>3.3142</v>
       </c>
       <c r="V13" t="n">
         <v>7.589000000000001</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4376</v>
+        <v>4.3365</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9681</v>
+        <v>0.867</v>
       </c>
       <c r="F14" t="n">
         <v>3.4696</v>
@@ -1546,10 +1546,10 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2888</v>
+        <v>0.1877</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1594</v>
+        <v>-0.2606</v>
       </c>
       <c r="U14" t="n">
         <v>0.4483</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4538</v>
+        <v>1.8121</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0989</v>
+        <v>-0.4066</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3549</v>
+        <v>2.2187</v>
       </c>
       <c r="G15" t="n">
         <v>3.5641</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2023</v>
+        <v>0.5606</v>
       </c>
       <c r="T15" t="n">
-        <v>0.864</v>
+        <v>0.3584</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3383</v>
+        <v>0.2021</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5545</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2129</v>
+        <v>1.2976</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5352</v>
+        <v>-0.6785</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7481</v>
+        <v>1.9761</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5528</v>
+        <v>0.313</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3098</v>
+        <v>-0.307</v>
       </c>
       <c r="I16" t="n">
-        <v>0.243</v>
+        <v>0.62</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8981</v>
+        <v>-0.551</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5989</v>
+        <v>-0.6319</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7007</v>
+        <v>0.0809</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.864</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2891</v>
+        <v>0.3249</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9437</v>
+        <v>0.5391</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9606</v>
+        <v>-0.1988</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4566</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4173</v>
+        <v>0.4126</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4959</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1509</v>
+        <v>1.2793</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0437</v>
+        <v>-0.9426</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1946</v>
+        <v>2.2218</v>
       </c>
       <c r="G17" t="n">
         <v>4.2738</v>
@@ -1780,13 +1780,13 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2047</v>
+        <v>-0.0764</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5364</v>
+        <v>-0.4352</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3316</v>
+        <v>0.3589</v>
       </c>
       <c r="V17" t="n">
         <v>-1.5507</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.142</v>
+        <v>0.6876</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7796</v>
+        <v>-0.4341</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9216</v>
+        <v>1.1217</v>
       </c>
       <c r="G18" t="n">
-        <v>0.313</v>
+        <v>1.5528</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.307</v>
+        <v>1.3098</v>
       </c>
       <c r="I18" t="n">
-        <v>0.62</v>
+        <v>0.243</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.551</v>
+        <v>0.8981</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6319</v>
+        <v>1.5989</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-0.7007</v>
       </c>
       <c r="M18" t="n">
-        <v>0.864</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3249</v>
+        <v>-0.2891</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5391</v>
+        <v>0.9437</v>
       </c>
       <c r="P18" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3544</v>
+        <v>0.4353</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7125</v>
+        <v>-0.3555</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3581</v>
+        <v>0.7909</v>
       </c>
       <c r="V18" t="n">
-        <v>2.16</v>
+        <v>-1.4959</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2765</v>
+        <v>0.4281</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4767</v>
+        <v>-0.4363</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2003</v>
+        <v>0.8643</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4344</v>
+        <v>1.6275</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8969</v>
+        <v>1.0883</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5375</v>
+        <v>0.5393</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9663</v>
+        <v>1.2522</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3722</v>
+        <v>1.9263</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5942</v>
+        <v>-0.6741</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4681</v>
+        <v>0.3753</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5247000000000001</v>
+        <v>-0.838</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9433</v>
+        <v>1.2134</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R19" t="n">
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2834</v>
+        <v>-0.5083</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2943</v>
+        <v>-0.5164</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0108</v>
+        <v>0.0081</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.0466</v>
+        <v>-0.8865</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.0466</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1476</v>
+        <v>0.3776</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7396</v>
+        <v>0.5779</v>
       </c>
       <c r="F20" t="n">
-        <v>0.592</v>
+        <v>-0.2003</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6275</v>
+        <v>2.4344</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0883</v>
+        <v>0.8969</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5393</v>
+        <v>1.5375</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2522</v>
+        <v>0.9663</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9263</v>
+        <v>0.3722</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>0.5942</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3753</v>
+        <v>1.4681</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.838</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2134</v>
+        <v>0.9433</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.084</v>
+        <v>-0.1823</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8198</v>
+        <v>-0.1931</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2642</v>
+        <v>0.0108</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8865</v>
+        <v>-3.0466</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8865</v>
+        <v>-3.0466</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4843</v>
+        <v>-0.1926</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2992</v>
+        <v>-2.1981</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8149</v>
+        <v>2.0056</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6995</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7615</v>
+        <v>-0.4698</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8803</v>
+        <v>-0.7792</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1187</v>
+        <v>0.3094</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.565</v>
+        <v>-1.3549</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.549</v>
+        <v>-1.4478</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.016</v>
+        <v>0.0929</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3212</v>
@@ -2170,13 +2170,13 @@
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4391</v>
+        <v>-0.229</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3026</v>
+        <v>-0.2015</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1365</v>
+        <v>-0.0275</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1851</v>
+        <v>-2.1228</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5139</v>
+        <v>-4.615</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3288</v>
+        <v>2.4922</v>
       </c>
       <c r="G23" t="n">
         <v>0.8427</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4996</v>
+        <v>0.5619</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0989</v>
+        <v>-0.2</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5985</v>
+        <v>0.762</v>
       </c>
       <c r="V23" t="n">
         <v>-2.16</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3696</v>
+        <v>-3.6263</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7099</v>
+        <v>-2.9121</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6596</v>
+        <v>-0.7141</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2355</v>
@@ -2326,13 +2326,13 @@
         <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>0.038</v>
+        <v>-0.2187</v>
       </c>
       <c r="T24" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.1196</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0447</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>0.6093</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.9221</v>
+        <v>2.922199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.6264</v>
+        <v>-12.6262</v>
       </c>
       <c r="F25" t="n">
-        <v>15.5486</v>
+        <v>15.5485</v>
       </c>
       <c r="G25" t="n">
         <v>14.5557</v>
@@ -2407,10 +2407,10 @@
         <v>-0.1378</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.3142</v>
+        <v>-3.3141</v>
       </c>
       <c r="U25" t="n">
-        <v>3.1762</v>
+        <v>3.1765</v>
       </c>
       <c r="V25" t="n">
         <v>-7.589099999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484274_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484274_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +653,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8003</v>
+        <v>1.5279</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.069</v>
+        <v>1.5279</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8694</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6283</v>
+        <v>1.5279</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2637</v>
+        <v>0.921</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3646</v>
+        <v>0.607</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4686</v>
+        <v>1.5279</v>
       </c>
       <c r="K3" t="n">
-        <v>0.165</v>
+        <v>0.921</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1597</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4287</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1341</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4284</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2943</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -704,12 +714,17 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +736,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3985</v>
+        <v>0.8003</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.12</v>
+        <v>-2.069</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5185</v>
+        <v>2.8694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.166</v>
+        <v>-0.6283</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0312</v>
+        <v>-0.2637</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1348</v>
+        <v>-0.3646</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0409</v>
+        <v>-0.4686</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0409</v>
+        <v>0.165</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1251</v>
+        <v>-0.1597</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0097</v>
+        <v>-0.4287</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1348</v>
+        <v>0.269</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>2.7348</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0371</v>
+        <v>-0.1341</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1609</v>
+        <v>-0.4284</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1981</v>
+        <v>0.2943</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -782,12 +797,17 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3156</v>
+        <v>0.3985</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.0533</v>
+        <v>-0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7377</v>
+        <v>0.5185</v>
       </c>
       <c r="G5" t="n">
-        <v>-5.9549</v>
+        <v>0.166</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.4332</v>
+        <v>0.0312</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5217</v>
+        <v>0.1348</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.3063</v>
+        <v>0.0409</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9763</v>
+        <v>0.0409</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.33</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6485</v>
+        <v>0.1251</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4569</v>
+        <v>-0.0097</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8083</v>
+        <v>0.1348</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1255</v>
+        <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6197</v>
+        <v>0.0371</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3127</v>
+        <v>-0.1609</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9325</v>
+        <v>0.1981</v>
       </c>
       <c r="V5" t="n">
-        <v>4.0428</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3283</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5929</v>
+        <v>-0.3156</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.211</v>
+        <v>-5.0533</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6181</v>
+        <v>4.7377</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4724</v>
+        <v>-5.9549</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3768</v>
+        <v>-3.4332</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8492</v>
+        <v>-2.5217</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1821</v>
+        <v>-5.3063</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2226</v>
+        <v>-1.9763</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-3.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6545</v>
+        <v>-0.6485</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1542</v>
+        <v>-1.4569</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8087</v>
+        <v>0.8083</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>3.1255</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4539</v>
+        <v>0.6197</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0522</v>
+        <v>-0.3127</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5061</v>
+        <v>0.9325</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1052</v>
+        <v>4.0428</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1052</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2415</v>
+        <v>-0.5929</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9553</v>
+        <v>-1.211</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2861</v>
+        <v>0.6181</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1775</v>
+        <v>0.4724</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.638</v>
+        <v>-0.3768</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5395</v>
+        <v>0.8492</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6933</v>
+        <v>-0.1821</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0192</v>
+        <v>-0.2226</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6741</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4842</v>
+        <v>0.6545</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6188</v>
+        <v>-0.1542</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1346</v>
+        <v>0.8087</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4547</v>
+        <v>0.4539</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.262</v>
+        <v>-0.0522</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1926</v>
+        <v>0.5061</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7059</v>
+        <v>-1.2415</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2093</v>
+        <v>-0.9553</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5034</v>
+        <v>-0.2861</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2836</v>
+        <v>-1.1775</v>
       </c>
       <c r="H8" t="n">
-        <v>0.065</v>
+        <v>-0.638</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3486</v>
+        <v>-0.5395</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6741</v>
+        <v>-0.6933</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.0192</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6095</v>
+        <v>-0.4842</v>
       </c>
       <c r="N8" t="n">
-        <v>0.065</v>
+        <v>-0.6188</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6745</v>
+        <v>0.1346</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.227</v>
+        <v>-0.4547</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1362</v>
+        <v>-0.1926</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,12 +1129,17 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7679</v>
+        <v>-1.7059</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1388</v>
+        <v>-2.2093</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6292</v>
+        <v>0.5034</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9944</v>
+        <v>-1.2836</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0645</v>
+        <v>0.065</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.3486</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5234</v>
+        <v>-0.6741</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2711</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7945</v>
+        <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.471</v>
+        <v>-0.6095</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.3356</v>
+        <v>0.065</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1354</v>
+        <v>-0.6745</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.227</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0022</v>
+        <v>-0.3631</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0838</v>
+        <v>0.1362</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1604</v>
+        <v>-1.7679</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2439</v>
+        <v>-1.1388</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9164</v>
+        <v>-0.6292</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1846</v>
+        <v>-2.9944</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.726</v>
+        <v>-2.0645</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4585</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4908</v>
+        <v>-0.5234</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1023</v>
+        <v>0.2711</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.7945</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6937</v>
+        <v>-2.471</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8283</v>
+        <v>-2.3356</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1346</v>
+        <v>-0.1354</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6335</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2236</v>
+        <v>0.0022</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4099</v>
+        <v>0.0838</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1317,72 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4731</v>
+        <v>-2.1604</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.918</v>
+        <v>-1.2439</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4449</v>
+        <v>-0.9164</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9175</v>
+        <v>-1.1846</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6204</v>
+        <v>-0.726</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2971</v>
+        <v>-0.4585</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5946</v>
+        <v>-0.4908</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1061</v>
+        <v>0.1023</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7007</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3228</v>
+        <v>-0.6937</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7265</v>
+        <v>-0.8283</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4037</v>
+        <v>0.1346</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>3.3208</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4189</v>
+        <v>0.6335</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4751</v>
+        <v>0.2236</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0562</v>
+        <v>0.4099</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1407,11 +1462,16 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,1004 +1483,1310 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7119</v>
+        <v>-4.001</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.3381</v>
+        <v>-5.4459</v>
       </c>
       <c r="F13" t="n">
-        <v>12.6264</v>
+        <v>1.4449</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.5559</v>
+        <v>-3.4454</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.812799999999999</v>
+        <v>-2.5413</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.743</v>
+        <v>-0.9041</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.892000000000001</v>
+        <v>-2.1226</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2173</v>
+        <v>-0.8148</v>
       </c>
       <c r="L13" t="n">
-        <v>-10.1094</v>
+        <v>-1.3077</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.6636</v>
+        <v>-1.3228</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.030100000000001</v>
+        <v>-1.7265</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3664</v>
+        <v>0.4037</v>
       </c>
       <c r="P13" t="n">
-        <v>3.9067</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6741</v>
+        <v>-3.1255</v>
       </c>
       <c r="R13" t="n">
-        <v>17.5807</v>
+        <v>3.3208</v>
       </c>
       <c r="S13" t="n">
-        <v>1.348</v>
+        <v>-0.4189</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.966</v>
+        <v>-0.4751</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3142</v>
+        <v>0.0562</v>
       </c>
       <c r="V13" t="n">
-        <v>7.589000000000001</v>
+        <v>-0.3321</v>
       </c>
       <c r="W13" t="n">
-        <v>10.1938</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.6048</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3365</v>
+        <v>-1.7119</v>
       </c>
       <c r="E14" t="n">
-        <v>0.867</v>
+        <v>-14.3381</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4696</v>
+        <v>12.6264</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2036</v>
+        <v>-14.5559</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5994</v>
+        <v>-7.8127</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6042</v>
+        <v>-6.743</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7451</v>
+        <v>-8.892100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6237</v>
+        <v>1.2174</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1214</v>
+        <v>-10.1094</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4585</v>
+        <v>-5.6636</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0243</v>
+        <v>-9.030099999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4828</v>
+        <v>3.3664</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>3.9067</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-13.6741</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>17.5807</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1877</v>
+        <v>1.348</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2606</v>
+        <v>-1.966</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4483</v>
+        <v>3.3142</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6642</v>
+        <v>7.589000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6642</v>
+        <v>10.1938</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-2.6048</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8121</v>
+        <v>4.3365</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4066</v>
+        <v>0.867</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2187</v>
+        <v>3.4696</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5641</v>
+        <v>5.2036</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7299</v>
+        <v>3.5994</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8342</v>
+        <v>1.6042</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3604</v>
+        <v>3.7451</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7396</v>
+        <v>3.6237</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6208</v>
+        <v>0.1214</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2037</v>
+        <v>1.4585</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0097</v>
+        <v>-0.0243</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2134</v>
+        <v>1.4828</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5606</v>
+        <v>0.1877</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3584</v>
+        <v>-0.2606</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2021</v>
+        <v>0.4483</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5545</v>
+        <v>-0.6642</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2976</v>
+        <v>1.8121</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6785</v>
+        <v>-0.4066</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9761</v>
+        <v>2.2187</v>
       </c>
       <c r="G16" t="n">
-        <v>0.313</v>
+        <v>3.5641</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.307</v>
+        <v>1.7299</v>
       </c>
       <c r="I16" t="n">
-        <v>0.62</v>
+        <v>1.8342</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.551</v>
+        <v>2.3604</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6319</v>
+        <v>1.7396</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>0.6208</v>
       </c>
       <c r="M16" t="n">
-        <v>0.864</v>
+        <v>1.2037</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3249</v>
+        <v>-0.0097</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5391</v>
+        <v>1.2134</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9767</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1988</v>
+        <v>0.5606</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.3584</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4126</v>
+        <v>0.2021</v>
       </c>
       <c r="V16" t="n">
-        <v>2.16</v>
+        <v>-0.5545</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2793</v>
+        <v>1.2976</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9426</v>
+        <v>-0.6785</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2218</v>
+        <v>1.9761</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2738</v>
+        <v>0.313</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3318</v>
+        <v>-0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>1.942</v>
+        <v>0.62</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9503</v>
+        <v>-0.551</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3561</v>
+        <v>-0.6319</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5942</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3235</v>
+        <v>0.864</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0243</v>
+        <v>0.3249</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3478</v>
+        <v>0.5391</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0764</v>
+        <v>-0.1988</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4352</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3589</v>
+        <v>0.4126</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5507</v>
+        <v>2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3321</v>
+        <v>2.4373</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6876</v>
+        <v>1.2793</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4341</v>
+        <v>-0.9426</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1217</v>
+        <v>2.2218</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5528</v>
+        <v>4.2738</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3098</v>
+        <v>2.3318</v>
       </c>
       <c r="I18" t="n">
-        <v>0.243</v>
+        <v>1.942</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8981</v>
+        <v>2.9503</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5989</v>
+        <v>2.3561</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7007</v>
+        <v>0.5942</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6546999999999999</v>
+        <v>1.3235</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2891</v>
+        <v>-0.0243</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9437</v>
+        <v>1.3478</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4353</v>
+        <v>-0.0764</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3555</v>
+        <v>-0.4352</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7909</v>
+        <v>0.3589</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4959</v>
+        <v>-1.5507</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4281</v>
+        <v>0.914</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4363</v>
+        <v>0.914</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8643</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6275</v>
+        <v>0.914</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0883</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5393</v>
+        <v>0.607</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2522</v>
+        <v>0.914</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9263</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6741</v>
+        <v>0.607</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3753</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.838</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2134</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5083</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5164</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0081</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3776</v>
+        <v>0.607</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5779</v>
+        <v>0.607</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2003</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4344</v>
+        <v>0.607</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8969</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5375</v>
+        <v>0.607</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9663</v>
+        <v>0.607</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3722</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5942</v>
+        <v>0.607</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4681</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5247000000000001</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1823</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0108</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.0466</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0466</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1926</v>
+        <v>0.4281</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1981</v>
+        <v>-0.4363</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0056</v>
+        <v>0.8643</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6995</v>
+        <v>1.6275</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6078</v>
+        <v>1.0883</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3073</v>
+        <v>0.5393</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.419</v>
+        <v>1.2522</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6971000000000001</v>
+        <v>1.9263</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1161</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7195</v>
+        <v>0.3753</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0893</v>
+        <v>-0.838</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8087</v>
+        <v>1.2134</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4698</v>
+        <v>-0.5083</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7792</v>
+        <v>-0.5164</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3094</v>
+        <v>0.0081</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3549</v>
+        <v>0.0806</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4478</v>
+        <v>-1.0411</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0929</v>
+        <v>1.1217</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3212</v>
+        <v>0.9458</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5526</v>
+        <v>1.3098</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7687</v>
+        <v>-0.364</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2463</v>
+        <v>0.2911</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6127</v>
+        <v>1.5989</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.3077</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0601</v>
+        <v>-0.2891</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.135</v>
+        <v>0.9437</v>
       </c>
       <c r="P22" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.229</v>
+        <v>0.4353</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2015</v>
+        <v>-0.3555</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0275</v>
+        <v>0.7909</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1228</v>
+        <v>-0.1926</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.615</v>
+        <v>-2.1981</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4922</v>
+        <v>2.0056</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8427</v>
+        <v>-0.6995</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2901</v>
+        <v>0.6078</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1328</v>
+        <v>-1.3073</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8207</v>
+        <v>-1.419</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2008</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6198</v>
+        <v>-2.1161</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6634</v>
+        <v>0.7195</v>
       </c>
       <c r="N23" t="n">
         <v>-0.0893</v>
       </c>
       <c r="O23" t="n">
-        <v>1.7527</v>
+        <v>0.8087</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5619</v>
+        <v>-0.4698</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2</v>
+        <v>-0.7792</v>
       </c>
       <c r="U23" t="n">
-        <v>0.762</v>
+        <v>0.3094</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6263</v>
+        <v>-0.5364</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9121</v>
+        <v>-0.3361</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7141</v>
+        <v>-0.2003</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2355</v>
+        <v>1.5204</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6015</v>
+        <v>0.5899</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.634</v>
+        <v>0.9305</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4717</v>
+        <v>0.0524</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.8381</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.0128</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7638</v>
+        <v>1.4681</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7634</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0004</v>
+        <v>0.9433</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R24" t="n">
         <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2187</v>
+        <v>-0.1823</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1196</v>
+        <v>-0.1931</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.0108</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6093</v>
+        <v>-3.0466</v>
       </c>
       <c r="W24" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>-3.0466</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-1.3549</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.4478</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0929</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.3212</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.5526</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.7687</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.2463</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.6127</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.07489999999999999</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.229</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.2015</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>J. LLORENTE GUILLEMI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.1228</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.615</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.4922</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8427</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2901</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.1328</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.8207</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.2008</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.6198</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.6634</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.0893</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.7527</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>E. MARTIN GASCON</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.6263</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-2.9121</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.7141</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.2355</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2.6015</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.634</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.4717</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.8381</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.7638</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.7634</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2187</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1196</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.09909999999999999</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484274_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>2.922199999999999</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E28" t="n">
         <v>-12.6262</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F28" t="n">
         <v>15.5485</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G28" t="n">
         <v>14.5557</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H28" t="n">
         <v>7.8127</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I28" t="n">
         <v>6.743</v>
       </c>
-      <c r="J25" t="n">
-        <v>5.663699999999999</v>
-      </c>
-      <c r="K25" t="n">
-        <v>9.0304</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="J28" t="n">
+        <v>5.663799999999998</v>
+      </c>
+      <c r="K28" t="n">
+        <v>9.030400000000002</v>
+      </c>
+      <c r="L28" t="n">
         <v>-3.3664</v>
       </c>
-      <c r="M25" t="n">
-        <v>8.891999999999999</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="M28" t="n">
+        <v>8.892000000000001</v>
+      </c>
+      <c r="N28" t="n">
         <v>-1.2177</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O28" t="n">
         <v>10.1095</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P28" t="n">
         <v>-3.907</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q28" t="n">
         <v>-17.5808</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R28" t="n">
         <v>13.6739</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S28" t="n">
         <v>-0.1378</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T28" t="n">
         <v>-3.3141</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U28" t="n">
         <v>3.1765</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V28" t="n">
         <v>-7.589099999999999</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W28" t="n">
         <v>2.6047</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X28" t="n">
         <v>-10.1938</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
